--- a/evac_by_zip/evac_by_zip_2026-08-07.xlsx
+++ b/evac_by_zip/evac_by_zip_2026-08-07.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="By ZIP Code" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Zone Detail" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By ZIP Code" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zone Detail" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,7 +578,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 305 addresses (across 49 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
+          <t>Address counts estimated via area-weighted polygon intersection of OEM evac zones × Census ZCTA boundaries. Source: Oregon OEM Fire_Evacuation_Areas_Public + Census TIGERweb ZCTA. NOTE: 305 addresses (across 0 zones) could not be placed on a ZIP code this run and are NOT included in the totals below — see the summary rows at the bottom of this table and the Evacuation Map's 'Unmatched zones' layer for detail.</t>
         </is>
       </c>
     </row>
